--- a/data/sp500_active/구성종목_2026-06-09.xlsx
+++ b/data/sp500_active/구성종목_2026-06-09.xlsx
@@ -32,7 +32,7 @@
     <t>비중(%)</t>
   </si>
   <si>
-    <t>ESM6 Index</t>
+    <t>ESM6 INDEX</t>
   </si>
   <si>
     <t>S&amp;P500 EMINI FUT JUN 2026</t>
